--- a/测试数据-课堂演示/excel/4-成绩-SE104_计算机网络.xlsx
+++ b/测试数据-课堂演示/excel/4-成绩-SE104_计算机网络.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +26,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,17 +58,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,8 +443,16 @@
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>学号</t>
@@ -439,146 +466,146 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AP1-平时作业
-满分:20</t>
+满分:30.0</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AP2-实验报告
-满分:20</t>
+满分:40.0</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>AP3-期中考试
-满分:20</t>
+          <t>AP3-课程设计
+满分:20.0</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>AP4-期末考试
-满分:40</t>
+满分:10.0</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>202301016</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>测试学生16</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16.6</v>
+        <v>33.2</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>17.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>35.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>202301017</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>测试学生17</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>16.6</v>
+        <v>24.9</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17.2</v>
+        <v>34.4</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>17.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>36.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>202301018</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>测试学生18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>17.2</v>
+        <v>25.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>17.8</v>
+        <v>35.6</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>18.4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>26</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>202301019</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>测试学生19</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>17.8</v>
+        <v>26.7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18.4</v>
+        <v>36.8</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>27.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>202301020</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>测试学生20</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>18.4</v>
+        <v>27.6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>13.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
